--- a/data/gravel/Megamo West 2025.xlsx
+++ b/data/gravel/Megamo West 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307442E5-97DD-C543-A5C3-66D9CE250ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF5B98-4875-D346-AAEF-3356C1391043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34920" yWindow="-21140" windowWidth="25020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6340" yWindow="540" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>https://www.megamo.com/biblioteca/arxius/MY26/WEST/images/WEST-01__MALVA26_D1-p-2000.png</t>
   </si>
 </sst>
 </file>
@@ -881,6 +884,9 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/Megamo West 2025.xlsx
+++ b/data/gravel/Megamo West 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF5B98-4875-D346-AAEF-3356C1391043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C210AB-9C21-5042-A4A3-E6EB8B7CF481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6340" yWindow="540" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -347,9 +347,6 @@
     <t>Megamo</t>
   </si>
   <si>
-    <t>euro</t>
-  </si>
-  <si>
     <t>West</t>
   </si>
   <si>
@@ -396,6 +393,15 @@
   </si>
   <si>
     <t>https://www.megamo.com/biblioteca/arxius/MY26/WEST/images/WEST-01__MALVA26_D1-p-2000.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Girona, Spain</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -770,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -790,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -839,7 +845,7 @@
         <v>86</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -847,7 +853,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>92</v>
@@ -868,7 +874,7 @@
         <v>97</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>98</v>
@@ -880,12 +886,12 @@
         <v>102</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -918,10 +924,10 @@
         <v>67</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S6" s="1">
         <v>1026</v>
@@ -935,7 +941,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1024,10 +1030,10 @@
         <v>67</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S8" s="1">
         <v>1028</v>
@@ -1083,10 +1089,10 @@
         <v>67</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S9" s="1">
         <v>1032</v>
@@ -1142,10 +1148,10 @@
         <v>67</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S10" s="1">
         <v>1041</v>
@@ -1251,7 +1257,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1">
         <v>67</v>
@@ -1340,10 +1346,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="1">
         <v>600</v>
@@ -1748,7 +1754,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1830,7 +1836,15 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Megamo West 2025.xlsx
+++ b/data/gravel/Megamo West 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C210AB-9C21-5042-A4A3-E6EB8B7CF481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD61B83-E109-6F45-8BFD-DCB60B751E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -402,6 +402,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -776,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1700,150 +1718,180 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>27.2</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>121</v>
       </c>
     </row>
